--- a/projects/2025-a-smoke-screen/outputs/result2.xlsx
+++ b/projects/2025-a-smoke-screen/outputs/result2.xlsx
@@ -602,31 +602,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>145</v>
+        <v>145.0320643620986</v>
       </c>
       <c r="C4" t="n">
         <v>140</v>
       </c>
       <c r="D4" t="n">
-        <v>2689.112528119042</v>
+        <v>2685.73189502174</v>
       </c>
       <c r="E4" t="n">
-        <v>-681.6916340248658</v>
+        <v>-682.0875374912021</v>
       </c>
       <c r="F4" t="n">
         <v>700</v>
       </c>
       <c r="G4" t="n">
-        <v>1488.724904089449</v>
+        <v>1483.177227492443</v>
       </c>
       <c r="H4" t="n">
-        <v>158.8288290942975</v>
+        <v>158.9477567046382</v>
       </c>
       <c r="I4" t="n">
-        <v>163.1487257886341</v>
+        <v>161.6304763801048</v>
       </c>
       <c r="J4" t="n">
-        <v>5.873475214352602</v>
+        <v>5.911502261903031</v>
       </c>
     </row>
     <row r="5">
